--- a/YAM-load-planner-template.xlsx
+++ b/YAM-load-planner-template.xlsx
@@ -617,10 +617,11 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Same columns as the pier2pier cargo upload, so existing files work too.</t>
+          <t>Standard cargo-list columns, so cargo lists you already have in this layout work too.</t>
         </is>
       </c>
     </row>
